--- a/KatalonData/VerifyUINoCFCCTestData.xlsx
+++ b/KatalonData/VerifyUINoCFCCTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cloned-Project-Katalon\VPS-Katalon\KatalonData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01C8637-DB4C-45F4-A8DF-204E6C622B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF07A01-273E-40A3-9F25-98E4067BC49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16920" activeTab="1" xr2:uid="{B09A5AEA-02B2-4406-A6E2-23194C6B960B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B09A5AEA-02B2-4406-A6E2-23194C6B960B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="107">
   <si>
     <t>Notes</t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>2029</t>
   </si>
 </sst>
 </file>
@@ -723,12 +726,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5B3A090-036A-40B0-A9B9-346B67CB3963}">
   <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="28.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="28.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="28.85546875" style="1"/>
+    <col min="1" max="16384" width="28.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -820,7 +823,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -891,7 +894,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -962,7 +965,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1116,12 +1119,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CB0DF0-A72D-4935-A701-68E37F979488}">
   <dimension ref="A1:AD5"/>
-  <sheetFormatPr defaultColWidth="28.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="28.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="28.85546875" style="1"/>
+    <col min="1" max="16384" width="28.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1213,7 +1216,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -1245,7 +1248,7 @@
         <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>14</v>
@@ -1284,7 +1287,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -1316,7 +1319,7 @@
         <v>34</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>36</v>
@@ -1355,7 +1358,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>47</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>49</v>
@@ -1426,7 +1429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>60</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>62</v>

--- a/KatalonData/VerifyUINoCFCCTestData.xlsx
+++ b/KatalonData/VerifyUINoCFCCTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF07A01-273E-40A3-9F25-98E4067BC49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3729AA14-236C-421F-ADBA-358DE3BCF6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B09A5AEA-02B2-4406-A6E2-23194C6B960B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B09A5AEA-02B2-4406-A6E2-23194C6B960B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="110">
   <si>
     <t>Notes</t>
   </si>
@@ -75,9 +75,6 @@
     <t>12</t>
   </si>
   <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>9563 Elm Street</t>
   </si>
   <si>
@@ -355,6 +352,18 @@
   </si>
   <si>
     <t>2029</t>
+  </si>
+  <si>
+    <t>12/2026</t>
+  </si>
+  <si>
+    <t>6/2027</t>
+  </si>
+  <si>
+    <t>8/2028</t>
+  </si>
+  <si>
+    <t>2/2029</t>
   </si>
 </sst>
 </file>
@@ -736,76 +745,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>2</v>
@@ -817,21 +826,21 @@
         <v>4</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -855,128 +864,128 @@
         <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="W2" s="2">
         <v>54654701</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="AD2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="Q3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="W3" s="2">
         <v>54654701</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AC3" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>7</v>
@@ -985,126 +994,126 @@
         <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="Q4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="U4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="W4" s="2">
         <v>54654701</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="Q5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="W5" s="2">
         <v>54654701</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1129,76 +1138,76 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="W1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>2</v>
@@ -1210,21 +1219,21 @@
         <v>4</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -1248,128 +1257,128 @@
         <v>12</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="W2" s="2">
         <v>54654701</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="AD2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="Q3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="W3" s="2">
         <v>54654701</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AC3" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>7</v>
@@ -1378,126 +1387,126 @@
         <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="Q4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T4" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="U4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="W4" s="2">
         <v>54654701</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P5" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="Q5" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="W5" s="2">
         <v>54654701</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
